--- a/毕设论文/本次答辩提交材料_20260525/g_毕业要求达成度表_质量跟踪评价表/附件17_软工毕业要求达成度评价表_含质量跟踪表_待填写签字.xlsx
+++ b/毕设论文/本次答辩提交材料_20260525/g_毕业要求达成度表_质量跟踪评价表/附件17_软工毕业要求达成度评价表_含质量跟踪表_待填写签字.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vel/Work/RobotOS/Lerobot/robotdoc/undergraduate-thesis/答辩材料包_1120221303_俞乐楠/本次答辩提交材料_20260525/g_毕业要求达成度表_质量跟踪评价表/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vel/Work/RobotOS/Lerobot/robotdoc/毕设论文/本次答辩提交材料_20260525/g_毕业要求达成度表_质量跟踪评价表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6F6BB4-2954-A744-A3B8-61AB6337EAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A34C3D6-228F-6941-B5BE-833B3F8B9DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="680" windowWidth="14720" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="毕业要求达成度评价表(学生教师打分)" sheetId="1" r:id="rId1"/>
@@ -32,37 +32,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>北京理工大学本科生软件工程专业
 毕业设计（论文）毕业要求达成度评价表</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>学生姓名：</t>
-    </r>
-  </si>
-  <si>
     <t>学生签字：</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>导师姓名：</t>
-    </r>
   </si>
   <si>
     <t>导师签字：</t>
@@ -101,9 +77,6 @@
 毕业设计（论文）过程及质量跟踪评价表</t>
   </si>
   <si>
-    <t>学生学号：</t>
-  </si>
-  <si>
     <t>序号</t>
   </si>
   <si>
@@ -127,7 +100,7 @@
   <si>
     <t>毕业要求2．
 问题分析</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>2.4 能运用基本原理，借助文献研究等方法，分析复杂软件工程问题的影响因素，获得有效结论</t>
@@ -135,7 +108,7 @@
   <si>
     <t>毕业要求4．
 研究</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>4.1 能够基于科学原理，通过文献研究或软件工程的基本方法，调研和分析复杂软件工程问题的解决方案</t>
@@ -146,7 +119,7 @@
   <si>
     <t>毕业要求7．
 环境和可持续发展</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>7.1 知晓和理解环境保护和可持续发展的理念和内涵</t>
@@ -162,29 +135,29 @@
   </si>
   <si>
     <t>论文结构合理，内容充实、结论可信；参考文献引用正确</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>能够针对特定需求，完成软件系统部件或模块的需求分析和设计，并能够用形式化模型和文档等形式呈现软件系统解决方案和成果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>学生积极接受指导老师指导，至少2周进行一次直接指导，表现出主动学习和不断探索的习惯</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>能够进行软件系统分析与设计，在设计中体现创新意识</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>毕业要求10．
 沟通</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>毕业要求12．
 终身学习</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -216,7 +189,7 @@
       </rPr>
       <t xml:space="preserve">学号：1120221303       </t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -239,14 +212,41 @@
       </rPr>
       <t>王勇</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>学生姓名：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>俞乐楠</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>学生学号：1120221303</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,12 +292,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -441,7 +435,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -469,7 +463,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -478,28 +472,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -508,17 +502,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -586,6 +577,138 @@
         <a:xfrm>
           <a:off x="5842000" y="800100"/>
           <a:ext cx="736600" cy="416173"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="736600" cy="416173"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ABF65F6-8A00-FB44-8400-5010DBFF38D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5842000" y="800100"/>
+          <a:ext cx="736600" cy="416173"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>45297</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31AD27DA-38D5-0439-5D09-1CA5CBCACD31}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5842000" y="1181100"/>
+          <a:ext cx="723900" cy="426297"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>108091</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{708D3DCB-E829-9B49-F7F6-F0BC0CB77EA7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4914900" y="1384300"/>
+          <a:ext cx="787400" cy="463691"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -903,47 +1026,47 @@
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1">
       <c r="A2" s="15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
       <c r="D2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="2"/>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="55" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="55" customHeight="1">
       <c r="A6" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C6" s="7">
         <v>15</v>
@@ -951,14 +1074,16 @@
       <c r="D6" s="8">
         <v>4</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="55" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" s="7">
         <v>20</v>
@@ -966,14 +1091,16 @@
       <c r="D7" s="8">
         <v>4</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="40.25" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C8" s="7">
         <v>20</v>
@@ -981,14 +1108,16 @@
       <c r="D8" s="8">
         <v>4</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="39.75" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" s="7">
         <v>10</v>
@@ -996,14 +1125,16 @@
       <c r="D9" s="8">
         <v>4</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="69.75" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C10" s="7">
         <v>10</v>
@@ -1011,14 +1142,16 @@
       <c r="D10" s="8">
         <v>4</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="55" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" s="7">
         <v>15</v>
@@ -1026,14 +1159,16 @@
       <c r="D11" s="8">
         <v>4</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="55" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="7">
         <v>10</v>
@@ -1041,15 +1176,17 @@
       <c r="D12" s="8">
         <v>4</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="55" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" s="17">
         <f>ROUND((C6*(D6+E6)+C7*(D7+E7)+C8*(D8+E8)+C9*(D9+E9)+C10*(D10+E10)+C11*(E11+E11)+C12*(D12+E12))/8,0)</f>
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -1057,12 +1194,12 @@
     </row>
     <row r="16" spans="1:5" ht="20.75" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.5" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -1071,7 +1208,7 @@
     </row>
     <row r="18" spans="1:5" ht="35" customHeight="1">
       <c r="A18" s="20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -1094,7 +1231,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:B3"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="B13:E13">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
@@ -1123,7 +1260,7 @@
   <sheetData>
     <row r="2" spans="1:5" ht="63.75" customHeight="1">
       <c r="A2" s="21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -1131,127 +1268,139 @@
       <c r="E2" s="21"/>
     </row>
     <row r="3" spans="1:5" ht="30" customHeight="1">
-      <c r="A3" s="16" t="s">
-        <v>1</v>
+      <c r="A3" s="15" t="s">
+        <v>38</v>
       </c>
       <c r="B3" s="16"/>
-      <c r="C3" s="25" t="s">
-        <v>15</v>
+      <c r="C3" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1">
-      <c r="A4" s="16" t="s">
-        <v>3</v>
+      <c r="A4" s="15" t="s">
+        <v>37</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="25" t="s">
-        <v>4</v>
+      <c r="C4" s="23" t="s">
+        <v>2</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
     </row>
     <row r="6" spans="1:5" ht="40" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="24"/>
+        <v>5</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" spans="1:5" ht="45" customHeight="1">
       <c r="A7" s="11">
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" s="7">
         <v>25</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="D7" s="24">
+        <v>4</v>
+      </c>
+      <c r="E7" s="24"/>
     </row>
     <row r="8" spans="1:5" ht="45" customHeight="1">
       <c r="A8" s="11">
         <v>2</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" s="7">
         <v>20</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
+      <c r="D8" s="24">
+        <v>4</v>
+      </c>
+      <c r="E8" s="24"/>
     </row>
     <row r="9" spans="1:5" ht="45" customHeight="1">
       <c r="A9" s="11">
         <v>3</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" s="7">
         <v>10</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="D9" s="24">
+        <v>4</v>
+      </c>
+      <c r="E9" s="24"/>
     </row>
     <row r="10" spans="1:5" ht="65.25" customHeight="1">
       <c r="A10" s="11">
         <v>4</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" s="7">
         <v>25</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
+      <c r="D10" s="24">
+        <v>4</v>
+      </c>
+      <c r="E10" s="24"/>
     </row>
     <row r="11" spans="1:5" ht="53.25" customHeight="1">
       <c r="A11" s="11">
         <v>5</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C11" s="7">
         <v>10</v>
       </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
+      <c r="D11" s="24">
+        <v>4</v>
+      </c>
+      <c r="E11" s="24"/>
     </row>
     <row r="12" spans="1:5" ht="45" customHeight="1">
       <c r="A12" s="11">
         <v>6</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C12" s="7">
         <v>10</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
+      <c r="D12" s="24">
+        <v>4</v>
+      </c>
+      <c r="E12" s="24"/>
     </row>
     <row r="13" spans="1:5" ht="45" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" s="17">
         <f>ROUND((C7*D7+C8*D8+C9*D9+C10*D10+C11*D11+C12*D12)/4,0)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -1259,12 +1408,12 @@
     </row>
     <row r="15" spans="1:5" ht="35" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="35" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -1272,7 +1421,7 @@
     </row>
     <row r="17" spans="1:5" ht="35" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -1288,12 +1437,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A17:E17"/>
@@ -1303,8 +1446,14 @@
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="B13:E13">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>0</formula>
@@ -1320,5 +1469,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>